--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eirar\Polla\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D242801-2D2A-4887-A195-E4CDE1B12B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E233505-551D-487E-A222-9AB7FF89A01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>vs</t>
   </si>
@@ -54,6 +54,21 @@
   </si>
   <si>
     <t>Semi 2</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -540,18 +555,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B1:I138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.53125" customWidth="1"/>
-    <col min="2" max="2" width="14.46484375" customWidth="1"/>
-    <col min="3" max="3" width="3.53125" customWidth="1"/>
-    <col min="4" max="4" width="14.796875" customWidth="1"/>
-    <col min="8" max="8" width="13.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
@@ -559,36 +574,44 @@
       <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa España</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="1"/>
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H3" s="5" t="str">
         <f>"Pasa "&amp; D3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Francia</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="9"/>
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
@@ -596,27 +619,31 @@
       <c r="D6" s="8"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Inglaterra</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="1"/>
+    <row r="7" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H7" s="5" t="str">
         <f>"Pasa "&amp; D7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Argentina</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
       <c r="D8" s="3"/>
@@ -624,339 +651,339 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H55"/>
       <c r="I55"/>
     </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H56"/>
       <c r="I56"/>
     </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H57"/>
       <c r="I57"/>
     </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H58"/>
       <c r="I58"/>
     </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H59"/>
       <c r="I59"/>
     </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H60"/>
       <c r="I60"/>
     </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H61"/>
       <c r="I61"/>
     </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H62"/>
       <c r="I62"/>
     </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H63"/>
       <c r="I63"/>
     </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H64"/>
       <c r="I64"/>
     </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H65"/>
       <c r="I65"/>
     </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H66"/>
       <c r="I66"/>
     </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H67"/>
       <c r="I67"/>
     </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H68"/>
       <c r="I68"/>
     </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H69"/>
       <c r="I69"/>
     </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H70"/>
       <c r="I70"/>
     </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H71"/>
       <c r="I71"/>
     </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H72"/>
       <c r="I72"/>
     </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H73"/>
       <c r="I73"/>
     </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H74"/>
       <c r="I74"/>
     </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H75"/>
       <c r="I75"/>
     </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H76"/>
       <c r="I76"/>
     </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H77"/>
       <c r="I77"/>
     </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H78"/>
       <c r="I78"/>
     </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H79"/>
       <c r="I79"/>
     </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H80"/>
       <c r="I80"/>
     </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H81"/>
       <c r="I81"/>
     </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H82"/>
       <c r="I82"/>
     </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H83"/>
       <c r="I83"/>
     </row>
-    <row r="84" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H84"/>
       <c r="I84"/>
     </row>
-    <row r="85" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H85"/>
       <c r="I85"/>
     </row>
-    <row r="86" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H86"/>
       <c r="I86"/>
     </row>
-    <row r="87" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H87"/>
       <c r="I87"/>
     </row>
-    <row r="88" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H88"/>
       <c r="I88"/>
     </row>
-    <row r="89" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H89"/>
       <c r="I89"/>
     </row>
-    <row r="90" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H90"/>
       <c r="I90"/>
     </row>
-    <row r="91" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H91"/>
       <c r="I91"/>
     </row>
-    <row r="92" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H96"/>
       <c r="I96"/>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H97"/>
       <c r="I97"/>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H98"/>
       <c r="I98"/>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H99"/>
       <c r="I99"/>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H100"/>
       <c r="I100"/>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H101"/>
       <c r="I101"/>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H102"/>
       <c r="I102"/>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H103"/>
       <c r="I103"/>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="104" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H104"/>
       <c r="I104"/>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="105" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H105"/>
       <c r="I105"/>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="106" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H106"/>
       <c r="I106"/>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="107" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H107"/>
       <c r="I107"/>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="108" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H108"/>
       <c r="I108"/>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="109" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H109"/>
       <c r="I109"/>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="110" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="111" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H111"/>
       <c r="I111"/>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="112" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H112"/>
       <c r="I112"/>
     </row>
-    <row r="113" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="113" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H113"/>
       <c r="I113"/>
     </row>
-    <row r="114" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="114" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H114"/>
       <c r="I114"/>
     </row>
-    <row r="115" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="115" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H115"/>
       <c r="I115"/>
     </row>
-    <row r="116" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="116" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H116"/>
       <c r="I116"/>
     </row>
-    <row r="117" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="117" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H117"/>
       <c r="I117"/>
     </row>
-    <row r="118" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="118" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H118"/>
       <c r="I118"/>
     </row>
-    <row r="119" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="119" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H119"/>
       <c r="I119"/>
     </row>
-    <row r="120" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="120" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H120"/>
       <c r="I120"/>
     </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="121" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H121"/>
       <c r="I121"/>
     </row>
-    <row r="122" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="122" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H122"/>
       <c r="I122"/>
     </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="123" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H123"/>
       <c r="I123"/>
     </row>
-    <row r="124" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="124" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H124"/>
       <c r="I124"/>
     </row>
-    <row r="125" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="125" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H125"/>
       <c r="I125"/>
     </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="126" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H126"/>
       <c r="I126"/>
     </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="127" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H127"/>
       <c r="I127"/>
     </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="128" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H128"/>
       <c r="I128"/>
     </row>
-    <row r="129" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="129" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H129"/>
       <c r="I129"/>
     </row>
-    <row r="130" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="130" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H130"/>
       <c r="I130"/>
     </row>
-    <row r="131" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="131" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H131"/>
       <c r="I131"/>
     </row>
-    <row r="132" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="132" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H132"/>
       <c r="I132"/>
     </row>
-    <row r="133" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="133" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H133"/>
       <c r="I133"/>
     </row>
-    <row r="134" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="134" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H134"/>
       <c r="I134"/>
     </row>
-    <row r="135" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="135" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H135"/>
       <c r="I135"/>
     </row>
-    <row r="136" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="136" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H136"/>
       <c r="I136"/>
     </row>
-    <row r="137" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="137" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H137"/>
       <c r="I137"/>
     </row>
-    <row r="138" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="138" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H138"/>
       <c r="I138"/>
     </row>

--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E233505-551D-487E-A222-9AB7FF89A01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96122B35-C5E6-4780-AB4D-7A96ACDAA803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>vs</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Argentina</t>
-  </si>
-  <si>
-    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -599,13 +596,9 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="B4" s="9"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>

--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96122B35-C5E6-4780-AB4D-7A96ACDAA803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68DCAEE-6418-4E68-9228-E4483D5A7C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>vs</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Argentina</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -596,9 +599,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>

--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68DCAEE-6418-4E68-9228-E4483D5A7C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C41F154-8F89-4387-8E19-60B3E6246906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>vs</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Argentina</t>
-  </si>
-  <si>
-    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -599,13 +596,9 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="B4" s="9"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>

--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C41F154-8F89-4387-8E19-60B3E6246906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B82E7BD-DDED-4D1F-B95E-0B59C62C1F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>vs</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Argentina</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -596,9 +599,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>3</v>
       </c>

--- a/Pauta/E05Pauta.xlsx
+++ b/Pauta/E05Pauta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B82E7BD-DDED-4D1F-B95E-0B59C62C1F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1002324C-C16D-44A5-B8C5-46CE1C46A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-16530" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>vs</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Pasa España</t>
+  </si>
+  <si>
+    <t>Pasa Argentina</t>
   </si>
 </sst>
 </file>
@@ -644,9 +647,13 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="I8" s="5" t="s">
         <v>3</v>
       </c>
